--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487554_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487554_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0762</v>
+        <v>4.0553</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8051</v>
+        <v>3.6238</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2711</v>
+        <v>0.4315</v>
       </c>
       <c r="G3" t="n">
         <v>3.1126</v>
@@ -688,13 +688,13 @@
         <v>2.9377</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2287</v>
+        <v>-0.2497</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3068</v>
+        <v>-0.4882</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0781</v>
+        <v>0.2385</v>
       </c>
       <c r="V3" t="n">
         <v>-1.5495</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>M. BARTOLOME COBLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.89</v>
+        <v>2.2286</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6896</v>
+        <v>1.832</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.7996</v>
+        <v>0.3966</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.0665</v>
+        <v>0.3993</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4396</v>
+        <v>1.5461</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.5061</v>
+        <v>-1.1468</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4979</v>
+        <v>2.0014</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6603</v>
+        <v>1.9513</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1624</v>
+        <v>0.0501</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.5644</v>
+        <v>-1.6021</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2207</v>
+        <v>-0.4052</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.3437</v>
+        <v>-1.1969</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3709</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1543</v>
+        <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
-        <v>3.5253</v>
+        <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>4.9773</v>
+        <v>0.0044</v>
       </c>
       <c r="T4" t="n">
-        <v>5.0291</v>
+        <v>-0.3111</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0519</v>
+        <v>0.3155</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6083</v>
+        <v>1.8249</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3169</v>
+        <v>2.1003</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7086</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BARTOLOME COBLE</t>
+          <t>. SUAREZ HEVIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3844</v>
+        <v>2.1083</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9343</v>
+        <v>0.4998</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4501</v>
+        <v>1.6084</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3993</v>
+        <v>0.4262</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5461</v>
+        <v>1.3453</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1468</v>
+        <v>-0.9192</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0014</v>
+        <v>2.0293</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9513</v>
+        <v>2.0244</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0501</v>
+        <v>0.0048</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6021</v>
+        <v>-1.6031</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4052</v>
+        <v>-0.6791</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1969</v>
+        <v>-0.924</v>
       </c>
       <c r="P5" t="n">
+        <v>-0.1958</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-3.1336</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.9377</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.6614</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.2166</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.2166</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-1.9585</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.9585</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.1602</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.2088</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.8249</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.1003</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>. SUAREZ HEVIA</t>
+          <t>J. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2595</v>
+        <v>0.0526</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7045</v>
+        <v>-1.2091</v>
       </c>
       <c r="F6" t="n">
-        <v>1.555</v>
+        <v>1.2617</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4262</v>
+        <v>-0.7308</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3453</v>
+        <v>0.7597</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9192</v>
+        <v>-1.4905</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0293</v>
+        <v>-0.4016</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0244</v>
+        <v>0.9628</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0048</v>
+        <v>-1.3645</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6031</v>
+        <v>-0.3292</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6791</v>
+        <v>-0.2031</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.924</v>
+        <v>-0.1261</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1336</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9377</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8126</v>
+        <v>0.1958</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.1717</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2203</v>
+        <v>0.0241</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PEREZ RUIZ</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3567</v>
+        <v>0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6185</v>
+        <v>3.9265</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2617</v>
+        <v>-3.9065</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7308</v>
+        <v>-4.0665</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7597</v>
+        <v>0.4396</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4905</v>
+        <v>-4.5061</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4016</v>
+        <v>0.4979</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9628</v>
+        <v>1.6603</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3645</v>
+        <v>-1.1624</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3292</v>
+        <v>-4.5644</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2031</v>
+        <v>-1.2207</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1261</v>
+        <v>-3.3437</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>3.5253</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2135</v>
+        <v>2.1073</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2376</v>
+        <v>2.2661</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0241</v>
+        <v>-0.1588</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.3169</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0392</v>
+        <v>-0.71</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3583</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3975</v>
+        <v>-1.4776</v>
       </c>
       <c r="G8" t="n">
         <v>-2.2187</v>
@@ -1078,13 +1078,13 @@
         <v>1.9585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1546</v>
+        <v>0.1745</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2535</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4081</v>
+        <v>-0.4883</v>
       </c>
       <c r="V8" t="n">
         <v>0.5507</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2609</v>
+        <v>-1.0249</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3272</v>
+        <v>-1.2248</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0663</v>
+        <v>0.1999</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3082</v>
@@ -1156,13 +1156,13 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5402</v>
+        <v>-0.3042</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4158</v>
+        <v>-0.3135</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1244</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MIRANDA GARCIA</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4304</v>
+        <v>-1.3652</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8363</v>
+        <v>-0.7267</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2667</v>
+        <v>-0.6385</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7569</v>
+        <v>-2.9805</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8574000000000001</v>
+        <v>0.5812</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8995</v>
+        <v>-3.5617</v>
       </c>
       <c r="J10" t="n">
-        <v>0.745</v>
+        <v>-0.365</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0935</v>
+        <v>0.9187</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6515</v>
+        <v>-1.2836</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.5019</v>
+        <v>-2.6156</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.951</v>
+        <v>-0.3375</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.551</v>
+        <v>-2.2781</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.1751</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9792</v>
+        <v>2.3502</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3265</v>
+        <v>0.4402</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4623</v>
+        <v>0.8134</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1357</v>
+        <v>-0.3732</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>A. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.749</v>
+        <v>-1.9768</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.057</v>
+        <v>1.4503</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-3.4271</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9805</v>
+        <v>-2.7569</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5812</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.5617</v>
+        <v>-1.8995</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.365</v>
+        <v>0.745</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9187</v>
+        <v>0.0935</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2836</v>
+        <v>0.6515</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6156</v>
+        <v>-3.5019</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3375</v>
+        <v>-0.951</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.2781</v>
+        <v>-2.551</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1751</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1751</v>
+        <v>-0.9792</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3502</v>
+        <v>0.9792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9436</v>
+        <v>0.7802</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.517</v>
+        <v>1.0763</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4266</v>
+        <v>-0.2961</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.673</v>
+        <v>-6.287</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4286</v>
+        <v>-3.0426</v>
       </c>
       <c r="F12" t="n">
         <v>-3.2444</v>
@@ -1390,10 +1390,10 @@
         <v>0.5875</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2633</v>
+        <v>0.6493</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5891</v>
+        <v>0.9751</v>
       </c>
       <c r="U12" t="n">
         <v>-0.3258</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3277</v>
+        <v>2.327699999999999</v>
       </c>
       <c r="E13" t="n">
         <v>11.3864</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.0588</v>
+        <v>-9.058800000000002</v>
       </c>
       <c r="G13" t="n">
         <v>-15.2075</v>
       </c>
       <c r="H13" t="n">
-        <v>3.739299999999999</v>
+        <v>3.7393</v>
       </c>
       <c r="I13" t="n">
         <v>-18.9469</v>
       </c>
       <c r="J13" t="n">
-        <v>9.599</v>
+        <v>9.598999999999998</v>
       </c>
       <c r="K13" t="n">
         <v>10.5147</v>
@@ -1468,13 +1468,13 @@
         <v>20.564</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6551</v>
+        <v>4.655</v>
       </c>
       <c r="T13" t="n">
-        <v>5.328399999999999</v>
+        <v>5.3284</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6733999999999999</v>
+        <v>-0.6734</v>
       </c>
       <c r="V13" t="n">
         <v>6.025399999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.7035</v>
+        <v>11.8144</v>
       </c>
       <c r="E14" t="n">
-        <v>12.775</v>
+        <v>13.696</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0715</v>
+        <v>-1.8816</v>
       </c>
       <c r="G14" t="n">
         <v>15.6134</v>
@@ -1546,13 +1546,13 @@
         <v>2.546</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1058</v>
+        <v>-0.9948</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1704</v>
+        <v>-0.2494</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9354</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8249</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1716</v>
+        <v>3.9639</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5957</v>
+        <v>4.5724</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4241</v>
+        <v>-0.6085</v>
       </c>
       <c r="G15" t="n">
         <v>2.3602</v>
@@ -1624,13 +1624,13 @@
         <v>2.7419</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9324</v>
+        <v>-0.2752</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4991</v>
+        <v>0.4758</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5667</v>
+        <v>-0.751</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2754</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8095</v>
+        <v>-0.6997</v>
       </c>
       <c r="E16" t="n">
         <v>1.5856</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.395</v>
+        <v>-2.2853</v>
       </c>
       <c r="G16" t="n">
         <v>0.6499</v>
@@ -1702,13 +1702,13 @@
         <v>1.7626</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.5662</v>
       </c>
       <c r="T16" t="n">
         <v>0.6099</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2858</v>
+        <v>-1.1761</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7368</v>
+        <v>-1.7811</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3181</v>
+        <v>-1.5228</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4186</v>
+        <v>-0.2582</v>
       </c>
       <c r="G17" t="n">
         <v>0.4938</v>
@@ -1780,13 +1780,13 @@
         <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5047</v>
+        <v>-0.549</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3435</v>
+        <v>0.1388</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8482</v>
+        <v>-0.6878</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5507</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.3428</v>
+        <v>-2.8016</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1266</v>
+        <v>-1.6149</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2162</v>
+        <v>-1.1867</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2696</v>
@@ -1858,13 +1858,13 @@
         <v>2.7419</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3105</v>
+        <v>-0.7693</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4288</v>
+        <v>0.0829</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8817</v>
+        <v>-0.8522</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.2241</v>
+        <v>-5.3974</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4265</v>
+        <v>-3.7335</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7976</v>
+        <v>-1.6639</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1968</v>
@@ -1936,13 +1936,13 @@
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0891</v>
+        <v>-0.0842</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0882</v>
+        <v>-0.2188</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0009</v>
+        <v>0.1345</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1578</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.0896</v>
+        <v>-6.7439</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0263</v>
+        <v>-3.9239</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0634</v>
+        <v>-2.82</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4432</v>
@@ -2014,13 +2014,13 @@
         <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0797</v>
+        <v>-0.734</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2682</v>
+        <v>-0.1659</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8115</v>
+        <v>-0.5681</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2166</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.327700000000001</v>
+        <v>-1.645400000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>9.058799999999998</v>
+        <v>9.058900000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.3864</v>
+        <v>-10.7042</v>
       </c>
       <c r="G21" t="n">
         <v>15.2077</v>
@@ -2092,13 +2092,13 @@
         <v>13.7094</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.6551</v>
+        <v>-3.9727</v>
       </c>
       <c r="T21" t="n">
         <v>0.6733</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.3284</v>
+        <v>-4.6462</v>
       </c>
       <c r="V21" t="n">
         <v>-6.025399999999999</v>
